--- a/business-libraries/test-data/home_school/keyword_route.xlsx
+++ b/business-libraries/test-data/home_school/keyword_route.xlsx
@@ -448,16 +448,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KW_HS_01</v>
+        <v>HS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>家长投诉</v>
+        <v>投诉,举报,找校长</v>
       </c>
       <c r="C2" t="str">
-        <v>家长投诉相关；工作压力大；感觉疲惫</v>
+        <v>曝光,发到网上,教育局</v>
       </c>
       <c r="D2" t="str">
-        <v>开玩笑的表达；反讽</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>home_school</v>
@@ -472,36 +472,36 @@
         <v>red</v>
       </c>
       <c r="I2" t="str">
-        <v>家长投诉</v>
+        <v>冲突升级</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="K2" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="L2" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>教师在对话中表达家长投诉相关信号，触发家校沟通合作模块评估和工具推荐</v>
+        <v>家长表达投诉或维权意图，走保护通道</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KW_HS_02</v>
+        <v>HS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>家长不配合</v>
+        <v>家长不配合,不回消息,不管孩子</v>
       </c>
       <c r="C3" t="str">
-        <v>家长不配合相关；家长不配合表现</v>
+        <v>联系不上家长,家长不上心</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -510,22 +510,22 @@
         <v>home_school</v>
       </c>
       <c r="F3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H3" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I3" t="str">
-        <v>家长不配合</v>
+        <v>配合不足</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="K3" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,18 +537,18 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达家长不配合相关困扰，推荐对应自我照顾工具</v>
+        <v>家长配合度不足</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KW_HS_03</v>
+        <v>HS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>家长意见大</v>
+        <v>家长天天问,一直发消息</v>
       </c>
       <c r="C4" t="str">
-        <v>家长意见大相关；情绪不良</v>
+        <v>半夜发消息,反复确认</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -557,7 +557,7 @@
         <v>home_school</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
         <v>fuzzy</v>
@@ -566,36 +566,36 @@
         <v>yellow</v>
       </c>
       <c r="I4" t="str">
-        <v>家长意见大</v>
+        <v>焦虑过载</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="K4" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="L4" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>教师表达家长意见大相关信号，推荐同伴支持或自评</v>
+        <v>家长焦虑水平偏高</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KW_HS_04</v>
+        <v>HS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被举报</v>
+        <v>家长质疑,不信任,觉得我针对</v>
       </c>
       <c r="C5" t="str">
-        <v>被举报相关；无精打采</v>
+        <v>说我偏心,不相信老师</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -604,34 +604,34 @@
         <v>home_school</v>
       </c>
       <c r="F5" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H5" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I5" t="str">
-        <v>被举报</v>
+        <v>信任薄弱</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="K5" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>教师表达被举报相关信号，推荐认知类工具</v>
+        <v>家校信任基础薄弱</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/home_school/keyword_route.xlsx
+++ b/business-libraries/test-data/home_school/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>HS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>投诉,举报,找校长</v>
+        <v>投诉;举报;找校长</v>
       </c>
       <c r="C2" t="str">
-        <v>曝光,发到网上,教育局</v>
+        <v>曝光;发到网上;教育局</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>冲突升级</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>HS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>家长不配合,不回消息,不管孩子</v>
+        <v>家长不配合;不回消息;不管孩子</v>
       </c>
       <c r="C3" t="str">
-        <v>联系不上家长,家长不上心</v>
+        <v>联系不上家长;家长不上心</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>配合不足</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +537,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>家长配合度不足</v>
+        <v>家长参与效能不足</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>HS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>家长天天问,一直发消息</v>
+        <v>家长天天问;一直发消息</v>
       </c>
       <c r="C4" t="str">
-        <v>半夜发消息,反复确认</v>
+        <v>半夜发消息;反复确认</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>焦虑过载</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="K4" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>HS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>家长质疑,不信任,觉得我针对</v>
+        <v>家长质疑;不信任;觉得我针对</v>
       </c>
       <c r="C5" t="str">
-        <v>说我偏心,不相信老师</v>
+        <v>说我偏心;不相信老师</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,10 +616,10 @@
         <v>信任薄弱</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="K5" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>家校信任基础薄弱</v>
+        <v>家校信任关系薄弱</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/home_school/keyword_route.xlsx
+++ b/business-libraries/test-data/home_school/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>HS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>投诉;举报;找校长</v>
+        <v>投诉,举报,找校长</v>
       </c>
       <c r="C2" t="str">
-        <v>曝光;发到网上;教育局</v>
+        <v>曝光,发到网上,教育局</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>冲突升级</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="K2" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>HS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>家长不配合;不回消息;不管孩子</v>
+        <v>家长不配合,不回消息,不管孩子</v>
       </c>
       <c r="C3" t="str">
-        <v>联系不上家长;家长不上心</v>
+        <v>联系不上家长,家长不上心</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>配合不足</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="K3" t="str">
-        <v>HS_RX_04</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +537,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>家长参与效能不足</v>
+        <v>家长配合度不足</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>HS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>家长天天问;一直发消息</v>
+        <v>家长天天问,一直发消息</v>
       </c>
       <c r="C4" t="str">
-        <v>半夜发消息;反复确认</v>
+        <v>半夜发消息,反复确认</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>焦虑过载</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="K4" t="str">
-        <v>HS_RX_05</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>HS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>家长质疑;不信任;觉得我针对</v>
+        <v>家长质疑,不信任,觉得我针对</v>
       </c>
       <c r="C5" t="str">
-        <v>说我偏心;不相信老师</v>
+        <v>说我偏心,不相信老师</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,10 +616,10 @@
         <v>信任薄弱</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="K5" t="str">
-        <v>HS_RX_06</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>家校信任关系薄弱</v>
+        <v>家校信任基础薄弱</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/home_school/keyword_route.xlsx
+++ b/business-libraries/test-data/home_school/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>HS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>投诉,举报,找校长</v>
+        <v>投诉;举报;找校长</v>
       </c>
       <c r="C2" t="str">
-        <v>曝光,发到网上,教育局</v>
+        <v>曝光;发到网上;教育局</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>冲突升级</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S2</v>
       </c>
       <c r="K2" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>HS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>家长不配合,不回消息,不管孩子</v>
+        <v>家长不配合;不回消息;不管孩子</v>
       </c>
       <c r="C3" t="str">
-        <v>联系不上家长,家长不上心</v>
+        <v>联系不上家长;家长不上心</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>配合不足</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +537,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>家长配合度不足</v>
+        <v>家长参与效能不足</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>HS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>家长天天问,一直发消息</v>
+        <v>家长天天问;一直发消息</v>
       </c>
       <c r="C4" t="str">
-        <v>半夜发消息,反复确认</v>
+        <v>半夜发消息;反复确认</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>焦虑过载</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>HS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>家长质疑,不信任,觉得我针对</v>
+        <v>家长质疑;不信任;觉得我针对</v>
       </c>
       <c r="C5" t="str">
-        <v>说我偏心,不相信老师</v>
+        <v>说我偏心;不相信老师</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,10 +616,10 @@
         <v>信任薄弱</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="K5" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>家校信任基础薄弱</v>
+        <v>家校信任关系薄弱</v>
       </c>
     </row>
   </sheetData>
